--- a/public/robot-template.xlsx
+++ b/public/robot-template.xlsx
@@ -44,7 +44,7 @@
     <t>渠道</t>
   </si>
   <si>
-    <t>图像</t>
+    <t>头像</t>
   </si>
   <si>
     <t>当前资产</t>

--- a/public/robot-template.xlsx
+++ b/public/robot-template.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>用户id（uid)</t>
   </si>
@@ -53,19 +53,16 @@
     <t>初始资产</t>
   </si>
   <si>
-    <t>robot11</t>
+    <t>robot0989</t>
   </si>
   <si>
-    <t>lzx</t>
+    <t>hhb</t>
   </si>
   <si>
-    <t>dev</t>
+    <t>DEV</t>
   </si>
   <si>
     <t>https://xxx.png</t>
-  </si>
-  <si>
-    <t>robot12</t>
   </si>
 </sst>
 </file>
@@ -1220,8 +1217,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="7"/>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
     <col min="2" max="2" width="10.4444444444444" customWidth="1"/>
@@ -1258,7 +1255,7 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2">
-        <v>1212</v>
+        <v>11250989</v>
       </c>
       <c r="B2" t="s">
         <v>8</v>
@@ -1276,42 +1273,15 @@
         <v>11</v>
       </c>
       <c r="G2">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="H2">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3">
-        <v>2121</v>
-      </c>
-      <c r="B3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3">
-        <v>1000002</v>
-      </c>
-      <c r="D3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3">
-        <v>400</v>
-      </c>
-      <c r="H3">
-        <v>400</v>
+        <v>1000</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1" display="https://xxx.png"/>
-    <hyperlink ref="F3" r:id="rId1" display="https://xxx.png"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/public/robot-template.xlsx
+++ b/public/robot-template.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>用户id（uid)</t>
   </si>
@@ -35,13 +35,7 @@
     <t>账号标识</t>
   </si>
   <si>
-    <t>应用id（APPID）</t>
-  </si>
-  <si>
     <t>昵称</t>
-  </si>
-  <si>
-    <t>渠道</t>
   </si>
   <si>
     <t>头像</t>
@@ -53,13 +47,7 @@
     <t>初始资产</t>
   </si>
   <si>
-    <t>robot0989</t>
-  </si>
-  <si>
     <t>hhb</t>
-  </si>
-  <si>
-    <t>DEV</t>
   </si>
   <si>
     <t>https://xxx.png</t>
@@ -1217,17 +1205,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="7"/>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
     <col min="2" max="2" width="10.4444444444444" customWidth="1"/>
-    <col min="3" max="3" width="17.5555555555556" customWidth="1"/>
-    <col min="6" max="6" width="22.6666666666667" customWidth="1"/>
-    <col min="8" max="8" width="11.7777777777778" customWidth="1"/>
+    <col min="4" max="4" width="22.6666666666667" customWidth="1"/>
+    <col min="6" max="6" width="11.7777777777778" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1246,42 +1233,30 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2">
+        <v>11251033</v>
+      </c>
+      <c r="B2">
+        <v>1033</v>
+      </c>
+      <c r="C2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="D2" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2">
-        <v>11250989</v>
-      </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2">
-        <v>1000002</v>
-      </c>
-      <c r="D2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2">
+      <c r="E2">
         <v>1000</v>
       </c>
-      <c r="H2">
+      <c r="F2">
         <v>1000</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1" display="https://xxx.png"/>
+    <hyperlink ref="D2" r:id="rId1" display="https://xxx.png"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/public/robot-template.xlsx
+++ b/public/robot-template.xlsx
@@ -50,7 +50,7 @@
     <t>hhb</t>
   </si>
   <si>
-    <t>https://xxx.png</t>
+    <t>https://cdn.tiptop.bet/static/img/frame02.png</t>
   </si>
 </sst>
 </file>
@@ -1255,9 +1255,6 @@
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1" display="https://xxx.png"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
